--- a/data.mn/public/datasets/inbound-passengers-by-region.xlsx
+++ b/data.mn/public/datasets/inbound-passengers-by-region.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inbound Passengers by Region" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,579 +426,1093 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>region</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B2" t="n">
+        <v>1083</v>
+      </c>
+      <c r="C2" t="n">
+        <v>814</v>
+      </c>
+      <c r="D2" t="n">
+        <v>626</v>
+      </c>
+      <c r="E2" t="n">
+        <v>503</v>
+      </c>
+      <c r="F2" t="n">
+        <v>606</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12336</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1126</v>
+      </c>
+      <c r="K2" t="n">
+        <v>982</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1165</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1520</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1848</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2444</v>
+      </c>
+      <c r="P2" t="n">
+        <v>422</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>401</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1391</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1835</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1796</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>America</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="B3" t="n">
+        <v>15022</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15564</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16044</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14368</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16708</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21498</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22884</v>
+      </c>
+      <c r="I3" t="n">
+        <v>21323</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19131</v>
+      </c>
+      <c r="K3" t="n">
+        <v>19607</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21949</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24096</v>
+      </c>
+      <c r="N3" t="n">
+        <v>25767</v>
+      </c>
+      <c r="O3" t="n">
+        <v>27174</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1862</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2054</v>
+      </c>
+      <c r="R3" t="n">
+        <v>11086</v>
+      </c>
+      <c r="S3" t="n">
+        <v>17786</v>
+      </c>
+      <c r="T3" t="n">
+        <v>21498</v>
+      </c>
+      <c r="U3" t="n">
+        <v>25390</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>East Asia and the Pacific</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="B4" t="n">
+        <v>259130</v>
+      </c>
+      <c r="C4" t="n">
+        <v>291253</v>
+      </c>
+      <c r="D4" t="n">
+        <v>294144</v>
+      </c>
+      <c r="E4" t="n">
+        <v>298086</v>
+      </c>
+      <c r="F4" t="n">
+        <v>367161</v>
+      </c>
+      <c r="G4" t="n">
+        <v>432654</v>
+      </c>
+      <c r="H4" t="n">
+        <v>461035</v>
+      </c>
+      <c r="I4" t="n">
+        <v>362074</v>
+      </c>
+      <c r="J4" t="n">
+        <v>359397</v>
+      </c>
+      <c r="K4" t="n">
+        <v>320191</v>
+      </c>
+      <c r="L4" t="n">
+        <v>303255</v>
+      </c>
+      <c r="M4" t="n">
+        <v>345648</v>
+      </c>
+      <c r="N4" t="n">
+        <v>372876</v>
+      </c>
+      <c r="O4" t="n">
+        <v>390323</v>
+      </c>
+      <c r="P4" t="n">
+        <v>27806</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12799</v>
+      </c>
+      <c r="R4" t="n">
+        <v>103374</v>
+      </c>
+      <c r="S4" t="n">
+        <v>350738</v>
+      </c>
+      <c r="T4" t="n">
+        <v>540279</v>
+      </c>
+      <c r="U4" t="n">
+        <v>599997</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="B5" t="n">
+        <v>130455</v>
+      </c>
+      <c r="C5" t="n">
+        <v>144269</v>
+      </c>
+      <c r="D5" t="n">
+        <v>154612</v>
+      </c>
+      <c r="E5" t="n">
+        <v>148753</v>
+      </c>
+      <c r="F5" t="n">
+        <v>168826</v>
+      </c>
+      <c r="G5" t="n">
+        <v>150892</v>
+      </c>
+      <c r="H5" t="n">
+        <v>133010</v>
+      </c>
+      <c r="I5" t="n">
+        <v>123342</v>
+      </c>
+      <c r="J5" t="n">
+        <v>119969</v>
+      </c>
+      <c r="K5" t="n">
+        <v>120089</v>
+      </c>
+      <c r="L5" t="n">
+        <v>138152</v>
+      </c>
+      <c r="M5" t="n">
+        <v>164392</v>
+      </c>
+      <c r="N5" t="n">
+        <v>189161</v>
+      </c>
+      <c r="O5" t="n">
+        <v>205230</v>
+      </c>
+      <c r="P5" t="n">
+        <v>35931</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>21419</v>
+      </c>
+      <c r="R5" t="n">
+        <v>177833</v>
+      </c>
+      <c r="S5" t="n">
+        <v>260606</v>
+      </c>
+      <c r="T5" t="n">
+        <v>274040</v>
+      </c>
+      <c r="U5" t="n">
+        <v>299380</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Middle East</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="B6" t="n">
+        <v>1282</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1331</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1614</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1637</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2569</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2469</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3138</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4213</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3766</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4013</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3830</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3884</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4806</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5289</v>
+      </c>
+      <c r="P6" t="n">
+        <v>620</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1917</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4668</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8741</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10215</v>
+      </c>
+      <c r="U6" t="n">
+        <v>16394</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>South Asia</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="B7" t="n">
+        <v>1407</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1271</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1370</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1451</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1597</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7149</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2310</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2650</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2295</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2329</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2876</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3127</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3909</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="P7" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>643</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2157</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4349</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5997</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Stateless</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>111</v>
+      </c>
+      <c r="C8" t="n">
+        <v>260</v>
+      </c>
+      <c r="D8" t="n">
+        <v>387</v>
+      </c>
+      <c r="E8" t="n">
+        <v>52</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" t="n">
+        <v>36</v>
+      </c>
+      <c r="N8" t="n">
+        <v>39</v>
+      </c>
+      <c r="O8" t="n">
+        <v>37</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>бүс</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2025</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Америк</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>1699</v>
+        <v>15022</v>
       </c>
       <c r="C2" t="n">
+        <v>15564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16044</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14368</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16708</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21498</v>
+      </c>
+      <c r="H2" t="n">
+        <v>22884</v>
+      </c>
+      <c r="I2" t="n">
+        <v>21323</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19131</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19607</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21949</v>
+      </c>
+      <c r="M2" t="n">
+        <v>24096</v>
+      </c>
+      <c r="N2" t="n">
+        <v>25767</v>
+      </c>
+      <c r="O2" t="n">
+        <v>27174</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1862</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2054</v>
+      </c>
+      <c r="R2" t="n">
+        <v>11086</v>
+      </c>
+      <c r="S2" t="n">
+        <v>17786</v>
+      </c>
+      <c r="T2" t="n">
+        <v>21498</v>
+      </c>
+      <c r="U2" t="n">
         <v>25390</v>
-      </c>
-      <c r="D2" t="n">
-        <v>599997</v>
-      </c>
-      <c r="E2" t="n">
-        <v>299380</v>
-      </c>
-      <c r="F2" t="n">
-        <v>16394</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8334</v>
-      </c>
-      <c r="H2" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2024</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Африк</t>
+        </is>
       </c>
       <c r="B3" t="n">
+        <v>1083</v>
+      </c>
+      <c r="C3" t="n">
+        <v>814</v>
+      </c>
+      <c r="D3" t="n">
+        <v>626</v>
+      </c>
+      <c r="E3" t="n">
+        <v>503</v>
+      </c>
+      <c r="F3" t="n">
+        <v>606</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12336</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1457</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1126</v>
+      </c>
+      <c r="K3" t="n">
+        <v>982</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1165</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1520</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1848</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2444</v>
+      </c>
+      <c r="P3" t="n">
+        <v>422</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>401</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1391</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1835</v>
+      </c>
+      <c r="T3" t="n">
         <v>1796</v>
       </c>
-      <c r="C3" t="n">
-        <v>21498</v>
-      </c>
-      <c r="D3" t="n">
-        <v>540279</v>
-      </c>
-      <c r="E3" t="n">
-        <v>274040</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10215</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5997</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10</v>
+      <c r="U3" t="n">
+        <v>1699</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2023</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Европ</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>1835</v>
+        <v>130455</v>
       </c>
       <c r="C4" t="n">
-        <v>17786</v>
+        <v>144269</v>
       </c>
       <c r="D4" t="n">
-        <v>350738</v>
+        <v>154612</v>
       </c>
       <c r="E4" t="n">
+        <v>148753</v>
+      </c>
+      <c r="F4" t="n">
+        <v>168826</v>
+      </c>
+      <c r="G4" t="n">
+        <v>150892</v>
+      </c>
+      <c r="H4" t="n">
+        <v>133010</v>
+      </c>
+      <c r="I4" t="n">
+        <v>123342</v>
+      </c>
+      <c r="J4" t="n">
+        <v>119969</v>
+      </c>
+      <c r="K4" t="n">
+        <v>120089</v>
+      </c>
+      <c r="L4" t="n">
+        <v>138152</v>
+      </c>
+      <c r="M4" t="n">
+        <v>164392</v>
+      </c>
+      <c r="N4" t="n">
+        <v>189161</v>
+      </c>
+      <c r="O4" t="n">
+        <v>205230</v>
+      </c>
+      <c r="P4" t="n">
+        <v>35931</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>21419</v>
+      </c>
+      <c r="R4" t="n">
+        <v>177833</v>
+      </c>
+      <c r="S4" t="n">
         <v>260606</v>
       </c>
-      <c r="F4" t="n">
-        <v>8741</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4349</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9</v>
+      <c r="T4" t="n">
+        <v>274040</v>
+      </c>
+      <c r="U4" t="n">
+        <v>299380</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2022</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Зүүн Ази болон Номхон далайн орнууд</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>1391</v>
+        <v>259130</v>
       </c>
       <c r="C5" t="n">
-        <v>11086</v>
+        <v>291253</v>
       </c>
       <c r="D5" t="n">
+        <v>294144</v>
+      </c>
+      <c r="E5" t="n">
+        <v>298086</v>
+      </c>
+      <c r="F5" t="n">
+        <v>367161</v>
+      </c>
+      <c r="G5" t="n">
+        <v>432654</v>
+      </c>
+      <c r="H5" t="n">
+        <v>461035</v>
+      </c>
+      <c r="I5" t="n">
+        <v>362074</v>
+      </c>
+      <c r="J5" t="n">
+        <v>359397</v>
+      </c>
+      <c r="K5" t="n">
+        <v>320191</v>
+      </c>
+      <c r="L5" t="n">
+        <v>303255</v>
+      </c>
+      <c r="M5" t="n">
+        <v>345648</v>
+      </c>
+      <c r="N5" t="n">
+        <v>372876</v>
+      </c>
+      <c r="O5" t="n">
+        <v>390323</v>
+      </c>
+      <c r="P5" t="n">
+        <v>27806</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12799</v>
+      </c>
+      <c r="R5" t="n">
         <v>103374</v>
       </c>
-      <c r="E5" t="n">
-        <v>177833</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4668</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2157</v>
-      </c>
-      <c r="H5" t="n">
-        <v>11</v>
+      <c r="S5" t="n">
+        <v>350738</v>
+      </c>
+      <c r="T5" t="n">
+        <v>540279</v>
+      </c>
+      <c r="U5" t="n">
+        <v>599997</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2021</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ойрхи Дорнод</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>401</v>
+        <v>1282</v>
       </c>
       <c r="C6" t="n">
-        <v>2054</v>
+        <v>1331</v>
       </c>
       <c r="D6" t="n">
-        <v>12799</v>
+        <v>1614</v>
       </c>
       <c r="E6" t="n">
-        <v>21419</v>
+        <v>1637</v>
       </c>
       <c r="F6" t="n">
+        <v>2569</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2469</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3138</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4213</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3766</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4013</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3830</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3884</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4806</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5289</v>
+      </c>
+      <c r="P6" t="n">
+        <v>620</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1917</v>
       </c>
-      <c r="G6" t="n">
-        <v>643</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
+      <c r="R6" t="n">
+        <v>4668</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8741</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10215</v>
+      </c>
+      <c r="U6" t="n">
+        <v>16394</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2020</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Харьяалалгүй</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>422</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>1862</v>
+        <v>260</v>
       </c>
       <c r="D7" t="n">
-        <v>27806</v>
+        <v>387</v>
       </c>
       <c r="E7" t="n">
-        <v>35931</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>620</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
         <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>36</v>
+      </c>
+      <c r="N7" t="n">
+        <v>39</v>
+      </c>
+      <c r="O7" t="n">
+        <v>37</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>11</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2019</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Өмнөд Ази</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>2444</v>
+        <v>1407</v>
       </c>
       <c r="C8" t="n">
-        <v>27174</v>
+        <v>1271</v>
       </c>
       <c r="D8" t="n">
-        <v>390323</v>
+        <v>1370</v>
       </c>
       <c r="E8" t="n">
-        <v>205230</v>
+        <v>1451</v>
       </c>
       <c r="F8" t="n">
-        <v>5289</v>
+        <v>1597</v>
       </c>
       <c r="G8" t="n">
+        <v>7149</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2310</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2650</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2295</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2329</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2876</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3127</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3909</v>
+      </c>
+      <c r="O8" t="n">
         <v>6463</v>
       </c>
-      <c r="H8" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1848</v>
-      </c>
-      <c r="C9" t="n">
-        <v>25767</v>
-      </c>
-      <c r="D9" t="n">
-        <v>372876</v>
-      </c>
-      <c r="E9" t="n">
-        <v>189161</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4806</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3909</v>
-      </c>
-      <c r="H9" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1520</v>
-      </c>
-      <c r="C10" t="n">
-        <v>24096</v>
-      </c>
-      <c r="D10" t="n">
-        <v>345648</v>
-      </c>
-      <c r="E10" t="n">
-        <v>164392</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3884</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3127</v>
-      </c>
-      <c r="H10" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1165</v>
-      </c>
-      <c r="C11" t="n">
-        <v>21949</v>
-      </c>
-      <c r="D11" t="n">
-        <v>303255</v>
-      </c>
-      <c r="E11" t="n">
-        <v>138152</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3830</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2876</v>
-      </c>
-      <c r="H11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B12" t="n">
-        <v>982</v>
-      </c>
-      <c r="C12" t="n">
-        <v>19607</v>
-      </c>
-      <c r="D12" t="n">
-        <v>320191</v>
-      </c>
-      <c r="E12" t="n">
-        <v>120089</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4013</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2329</v>
-      </c>
-      <c r="H12" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1126</v>
-      </c>
-      <c r="C13" t="n">
-        <v>19131</v>
-      </c>
-      <c r="D13" t="n">
-        <v>359397</v>
-      </c>
-      <c r="E13" t="n">
-        <v>119969</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3766</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2295</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C14" t="n">
-        <v>21323</v>
-      </c>
-      <c r="D14" t="n">
-        <v>362074</v>
-      </c>
-      <c r="E14" t="n">
-        <v>123342</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4213</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2650</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1457</v>
-      </c>
-      <c r="C15" t="n">
-        <v>22884</v>
-      </c>
-      <c r="D15" t="n">
-        <v>461035</v>
-      </c>
-      <c r="E15" t="n">
-        <v>133010</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3138</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2310</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B16" t="n">
-        <v>12336</v>
-      </c>
-      <c r="C16" t="n">
-        <v>21498</v>
-      </c>
-      <c r="D16" t="n">
-        <v>432654</v>
-      </c>
-      <c r="E16" t="n">
-        <v>150892</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2469</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7149</v>
-      </c>
-      <c r="H16" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B17" t="n">
-        <v>606</v>
-      </c>
-      <c r="C17" t="n">
-        <v>16708</v>
-      </c>
-      <c r="D17" t="n">
-        <v>367161</v>
-      </c>
-      <c r="E17" t="n">
-        <v>168826</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2569</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1597</v>
-      </c>
-      <c r="H17" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B18" t="n">
-        <v>503</v>
-      </c>
-      <c r="C18" t="n">
-        <v>14368</v>
-      </c>
-      <c r="D18" t="n">
-        <v>298086</v>
-      </c>
-      <c r="E18" t="n">
-        <v>148753</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1637</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1451</v>
-      </c>
-      <c r="H18" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B19" t="n">
-        <v>626</v>
-      </c>
-      <c r="C19" t="n">
-        <v>16044</v>
-      </c>
-      <c r="D19" t="n">
-        <v>294144</v>
-      </c>
-      <c r="E19" t="n">
-        <v>154612</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1614</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1370</v>
-      </c>
-      <c r="H19" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B20" t="n">
-        <v>814</v>
-      </c>
-      <c r="C20" t="n">
-        <v>15564</v>
-      </c>
-      <c r="D20" t="n">
-        <v>291253</v>
-      </c>
-      <c r="E20" t="n">
-        <v>144269</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1331</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1271</v>
-      </c>
-      <c r="H20" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1083</v>
-      </c>
-      <c r="C21" t="n">
-        <v>15022</v>
-      </c>
-      <c r="D21" t="n">
-        <v>259130</v>
-      </c>
-      <c r="E21" t="n">
-        <v>130455</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1282</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1407</v>
-      </c>
-      <c r="H21" t="n">
-        <v>111</v>
+      <c r="P8" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>643</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2157</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4349</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5997</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8334</v>
       </c>
     </row>
   </sheetData>
